--- a/XLibur.Tests/Resource/Examples/Ranges/DefinedNames.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/DefinedNames.xlsx
@@ -400,7 +400,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="13.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="2.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="3.139196" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
@@ -465,8 +465,8 @@
   <x:dimension ref="A1:B4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="5.996339" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="4.139196" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="6.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="4.282054" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">

--- a/XLibur.Tests/Resource/Examples/Ranges/DefinedNames.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/DefinedNames.xlsx
@@ -409,6 +409,7 @@
       </x:c>
       <x:c r="B1" s="0">
         <x:f>COUNT(PeopleData)</x:f>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
@@ -417,6 +418,7 @@
       </x:c>
       <x:c r="B2" s="0">
         <x:f>PeopleCount</x:f>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
